--- a/artfynd/A 54081-2025 artfynd.xlsx
+++ b/artfynd/A 54081-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131913466</v>
       </c>
       <c r="B2" t="n">
-        <v>96157</v>
+        <v>96160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54081-2025 artfynd.xlsx
+++ b/artfynd/A 54081-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131913466</v>
       </c>
       <c r="B2" t="n">
-        <v>96160</v>
+        <v>96165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54081-2025 artfynd.xlsx
+++ b/artfynd/A 54081-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131913466</v>
       </c>
       <c r="B2" t="n">
-        <v>96208</v>
+        <v>96211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54081-2025 artfynd.xlsx
+++ b/artfynd/A 54081-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131913466</v>
       </c>
       <c r="B2" t="n">
-        <v>96211</v>
+        <v>96219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54081-2025 artfynd.xlsx
+++ b/artfynd/A 54081-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131913466</v>
       </c>
       <c r="B2" t="n">
-        <v>96219</v>
+        <v>96229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54081-2025 artfynd.xlsx
+++ b/artfynd/A 54081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131913466</v>
       </c>
       <c r="B2" t="n">
-        <v>96229</v>
+        <v>96306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,6 +769,418 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131913467</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78774</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sätramarkens naturreservat, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>562853</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6506324</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131913468</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111471</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sätramarkens naturreservat, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>562852</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6506326</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131913469</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sätramarkens naturreservat, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562852</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6506327</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129474308</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101227</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nedre Ågelsjö NO 545 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562868</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6506291</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Något enda ex</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägkant/slänt, lövskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström, Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54081-2025 artfynd.xlsx
+++ b/artfynd/A 54081-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131913466</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131913467</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131913468</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131913469</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,8 +1206,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129474308</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>